--- a/AI_Outcomes.xlsx
+++ b/AI_Outcomes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>OutcomeDate</t>
   </si>
@@ -40,16 +40,25 @@
     <t>20260328_063053</t>
   </si>
   <si>
+    <t>20260513_044158</t>
+  </si>
+  <si>
     <t>Negative Sentiment %</t>
   </si>
   <si>
     <t>0%</t>
   </si>
   <si>
+    <t>50%</t>
+  </si>
+  <si>
     <t>100%</t>
   </si>
   <si>
     <t>+100%</t>
+  </si>
+  <si>
+    <t>+50%</t>
   </si>
   <si>
     <t>WORSENED</t>
@@ -388,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -431,19 +440,42 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="G2" t="s">
+      <c r="E3" t="s">
         <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
